--- a/exports/LICI_full_report.xlsx
+++ b/exports/LICI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44715.55208333334</v>
+        <v>44718.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>391.05</v>
+        <v>383.1</v>
       </c>
       <c r="I2" t="n">
         <v>383.8781798639435</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.15</v>
+        <v>-5.11</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>5.31</v>
       </c>
       <c r="M2" t="n">
         <v>3.2</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.74</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44746.38541666666</v>
+        <v>44746.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>334.85</v>
+        <v>338.85</v>
       </c>
       <c r="I3" t="n">
         <v>338.0996344632917</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>12.59</v>
+        <v>11.55</v>
       </c>
       <c r="L3" t="n">
         <v>2.23</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>5.47</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44761.38541666666</v>
+        <v>44761.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>337.6</v>
+        <v>336.2</v>
       </c>
       <c r="I4" t="n">
         <v>337.374144270438</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.37</v>
+        <v>-0.78</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>4</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44785.55208333334</v>
+        <v>44789.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>333.4</v>
+        <v>341.25</v>
       </c>
       <c r="I5" t="n">
         <v>337.9422363457664</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>24</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.83</v>
+        <v>-1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>2.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0.89</v>
+        <v>1.54</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2.13</v>
       </c>
       <c r="O5" t="n">
         <v>-1.1</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>3.33</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>334.25</v>
+        <v>330.65</v>
       </c>
       <c r="I6" t="n">
         <v>331.2328175054429</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.05</v>
+        <v>-3.11</v>
       </c>
       <c r="L6" t="n">
-        <v>2.17</v>
+        <v>3.19</v>
       </c>
       <c r="M6" t="n">
         <v>-0</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>3.84</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44817.38541666666</v>
+        <v>44817.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>319.95</v>
+        <v>327.4</v>
       </c>
       <c r="I7" t="n">
         <v>325.344093679095</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>3.24</v>
+        <v>0.98</v>
       </c>
       <c r="L7" t="n">
         <v>1.19</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>3.79</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>317.65</v>
+        <v>315.7</v>
       </c>
       <c r="I8" t="n">
         <v>316.9788635360881</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.98</v>
+        <v>-3.57</v>
       </c>
       <c r="L8" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="M8" t="n">
         <v>0.8100000000000001</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>3.82</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44862.55208333334</v>
+        <v>44865.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>289.5</v>
+        <v>297.05</v>
       </c>
       <c r="I9" t="n">
         <v>295.7536570110973</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K9" t="n">
-        <v>8.300000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2.42</v>
       </c>
       <c r="N9" t="n">
         <v>1.93</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>2.6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>312.4</v>
+        <v>307.3</v>
       </c>
       <c r="I10" t="n">
         <v>310.3440267275136</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>5.17</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>0.86</v>
@@ -1011,7 +1130,7 @@
         <v>0.48</v>
       </c>
       <c r="N10" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.9</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>5.3</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44895.55208333334</v>
+        <v>44896.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>311</v>
+        <v>318.75</v>
       </c>
       <c r="I11" t="n">
         <v>315.2118075458127</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2</v>
+        <v>-3.73</v>
       </c>
       <c r="L11" t="n">
-        <v>2.29</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
         <v>0.61</v>
       </c>
       <c r="N11" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
         <v>-2.1</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.39</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>341.95</v>
+        <v>333.1</v>
       </c>
       <c r="I12" t="n">
         <v>337.8886946179141</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>7.28</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>2.21</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>10.85</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44929.38541666666</v>
+        <v>44929.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>350.8</v>
+        <v>358.6</v>
       </c>
       <c r="I13" t="n">
         <v>351.5715819185612</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.31</v>
+        <v>-7.66</v>
       </c>
       <c r="L13" t="n">
-        <v>6.62</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>0.76</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.45</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>342.7</v>
+        <v>337.1</v>
       </c>
       <c r="I14" t="n">
         <v>339.6014666188145</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.43</v>
+        <v>-6</v>
       </c>
       <c r="L14" t="n">
-        <v>5.28</v>
+        <v>6.05</v>
       </c>
       <c r="M14" t="n">
         <v>0.14</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.86</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>283.85</v>
+        <v>291.65</v>
       </c>
       <c r="I15" t="n">
         <v>287.2432244337191</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
-        <v>15.8</v>
+        <v>13.48</v>
       </c>
       <c r="L15" t="n">
         <v>2.18</v>
@@ -1296,7 +1475,7 @@
         <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>-1.71</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.55</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>291.4</v>
+        <v>287.25</v>
       </c>
       <c r="I16" t="n">
         <v>289.1491343115018</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.09</v>
+        <v>-1.51</v>
       </c>
       <c r="L16" t="n">
         <v>2.81</v>
@@ -1353,7 +1544,7 @@
         <v>0.6</v>
       </c>
       <c r="N16" t="n">
-        <v>1.21</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
         <v>3.65</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.03</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45050.55208333334</v>
+        <v>45051.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>269.55</v>
+        <v>274.65</v>
       </c>
       <c r="I17" t="n">
         <v>271.8925403315211</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K17" t="n">
-        <v>6.16</v>
+        <v>4.39</v>
       </c>
       <c r="L17" t="n">
         <v>1.78</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.93</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45100.55208333334</v>
+        <v>45103.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>304.75</v>
+        <v>303.55</v>
       </c>
       <c r="I18" t="n">
         <v>303.8438915266246</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K18" t="n">
-        <v>10.96</v>
+        <v>10.52</v>
       </c>
       <c r="L18" t="n">
         <v>1.88</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.2</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45127.55208333334</v>
+        <v>45128.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>307</v>
+        <v>312.95</v>
       </c>
       <c r="I19" t="n">
         <v>310.1862396466193</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.14</v>
+        <v>-3.1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>3.48</v>
       </c>
       <c r="M19" t="n">
         <v>0.71</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.19</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45190.38541666666</v>
+        <v>45190.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>320.95</v>
+        <v>319.7</v>
       </c>
       <c r="I20" t="n">
         <v>320.1625854243217</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="L20" t="n">
         <v>3.05</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.68</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45253.38541666666</v>
+        <v>45253.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>298.05</v>
+        <v>304.4</v>
       </c>
       <c r="I21" t="n">
         <v>301.6650994536641</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>62.83333333333334</v>
+        <v>63</v>
       </c>
       <c r="K21" t="n">
-        <v>6.77</v>
+        <v>4.79</v>
       </c>
       <c r="L21" t="n">
         <v>0.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.53</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>386.5</v>
+        <v>372.75</v>
       </c>
       <c r="I22" t="n">
         <v>373.7065525369745</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>26.97</v>
+        <v>22.45</v>
       </c>
       <c r="L22" t="n">
         <v>2.14</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.1</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45287.38541666666</v>
+        <v>45287.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>395.25</v>
+        <v>400.6</v>
       </c>
       <c r="I23" t="n">
         <v>396.1346760902962</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.04</v>
+        <v>-7.47</v>
       </c>
       <c r="L23" t="n">
-        <v>7.61</v>
+        <v>8.26</v>
       </c>
       <c r="M23" t="n">
         <v>5.25</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>441.85</v>
+        <v>427</v>
       </c>
       <c r="I24" t="n">
         <v>429.1966211581014</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>10.3</v>
+        <v>6.59</v>
       </c>
       <c r="L24" t="n">
         <v>2.71</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.08</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>455.8</v>
+        <v>467.45</v>
       </c>
       <c r="I25" t="n">
         <v>466.9090131757441</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.74</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>9.26</v>
+        <v>11.19</v>
       </c>
       <c r="M25" t="n">
         <v>0.83</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>494.65</v>
+        <v>481.5</v>
       </c>
       <c r="I26" t="n">
         <v>489.6474664915929</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>5.82</v>
+        <v>3.01</v>
       </c>
       <c r="L26" t="n">
         <v>3.22</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.49</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45383.38541666666</v>
+        <v>45383.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>462.65</v>
+        <v>474.85</v>
       </c>
       <c r="I27" t="n">
         <v>464.3443497127688</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>3.91</v>
+        <v>1.38</v>
       </c>
       <c r="L27" t="n">
         <v>3.39</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.35</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>478.3</v>
+        <v>459.35</v>
       </c>
       <c r="I28" t="n">
         <v>466.356095494054</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K28" t="n">
-        <v>0.73</v>
+        <v>-3.26</v>
       </c>
       <c r="L28" t="n">
         <v>4.11</v>
@@ -2037,7 +2372,7 @@
         <v>1.69</v>
       </c>
       <c r="N28" t="n">
-        <v>2.02</v>
+        <v>4.39</v>
       </c>
       <c r="O28" t="n">
         <v>5.99</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.18</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45426.55208333334</v>
+        <v>45427.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>456.8</v>
+        <v>474.05</v>
       </c>
       <c r="I29" t="n">
         <v>461.7726317484892</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.2</v>
       </c>
       <c r="L29" t="n">
         <v>4.75</v>
@@ -2094,7 +2441,7 @@
         <v>1.79</v>
       </c>
       <c r="N29" t="n">
-        <v>4.59</v>
+        <v>6.32</v>
       </c>
       <c r="O29" t="n">
         <v>-4.39</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>8.02</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>521</v>
+        <v>459.7</v>
       </c>
       <c r="I30" t="n">
         <v>480.7486818393455</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>9.9</v>
+        <v>-3.03</v>
       </c>
       <c r="L30" t="n">
-        <v>3.89</v>
+        <v>9.31</v>
       </c>
       <c r="M30" t="n">
-        <v>0.49</v>
+        <v>1.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.2</v>
+        <v>12.42</v>
       </c>
       <c r="O30" t="n">
         <v>6.32</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>16.04</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45457.38541666666</v>
+        <v>45457.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>511.75</v>
+        <v>518.75</v>
       </c>
       <c r="I31" t="n">
         <v>515.8844222065144</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-11.32</v>
+        <v>-12.85</v>
       </c>
       <c r="L31" t="n">
-        <v>13.18</v>
+        <v>13.9</v>
       </c>
       <c r="M31" t="n">
         <v>1.68</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>577.95</v>
+        <v>539.45</v>
       </c>
       <c r="I32" t="n">
         <v>542.2365278204393</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>49</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K32" t="n">
-        <v>11.41</v>
+        <v>3.99</v>
       </c>
       <c r="L32" t="n">
         <v>7.5</v>
       </c>
       <c r="M32" t="n">
-        <v>1.27</v>
+        <v>2.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.21</v>
+        <v>6.25</v>
       </c>
       <c r="O32" t="n">
         <v>5.81</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.03</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45624.38541666666</v>
+        <v>45624.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>453.55</v>
+        <v>459.65</v>
       </c>
       <c r="I33" t="n">
         <v>456.9444223183585</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>115</v>
+        <v>115.1666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>15.92</v>
+        <v>14.79</v>
       </c>
       <c r="L33" t="n">
         <v>5.05</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45636.38541666666</v>
+        <v>45636.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>463.45</v>
+        <v>462.9</v>
       </c>
       <c r="I34" t="n">
         <v>463.0022208065893</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="L34" t="n">
         <v>1.36</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.29</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>417.65</v>
+        <v>421.5</v>
       </c>
       <c r="I35" t="n">
         <v>418.6013241889821</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>9.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="L35" t="n">
         <v>0.48</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.8</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>408.45</v>
+        <v>401.5</v>
       </c>
       <c r="I36" t="n">
         <v>402.286912821882</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.1</v>
+        <v>-4.74</v>
       </c>
       <c r="L36" t="n">
-        <v>3.16</v>
+        <v>5.04</v>
       </c>
       <c r="M36" t="n">
         <v>-0</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.27</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45689.38541666666</v>
+        <v>45689.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>409</v>
+        <v>414.3</v>
       </c>
       <c r="I37" t="n">
         <v>414.0357446899565</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.87</v>
+        <v>-3.19</v>
       </c>
       <c r="L37" t="n">
         <v>5.79</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.81</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>394.55</v>
+        <v>386.1</v>
       </c>
       <c r="I38" t="n">
         <v>391.7274996680023</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.77</v>
+        <v>-6.81</v>
       </c>
       <c r="L38" t="n">
-        <v>4.91</v>
+        <v>6.82</v>
       </c>
       <c r="M38" t="n">
         <v>0.47</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.95</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>370.1</v>
+        <v>379.6</v>
       </c>
       <c r="I39" t="n">
         <v>376.349099399638</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K39" t="n">
-        <v>4.14</v>
+        <v>1.68</v>
       </c>
       <c r="L39" t="n">
         <v>3.03</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.67</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>387.9</v>
+        <v>370.9</v>
       </c>
       <c r="I40" t="n">
         <v>380.0942444547559</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>2.19</v>
+        <v>-2.29</v>
       </c>
       <c r="L40" t="n">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="M40" t="n">
-        <v>0.64</v>
+        <v>6.17</v>
       </c>
       <c r="N40" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
         <v>2.51</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>6</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>391.8</v>
+        <v>400.9</v>
       </c>
       <c r="I41" t="n">
         <v>393.1647457924829</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.63</v>
+        <v>-8.09</v>
       </c>
       <c r="L41" t="n">
-        <v>6.27</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>3.14</v>
       </c>
       <c r="N41" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="O41" t="n">
         <v>-2.9</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>5.79</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>387.45</v>
+        <v>382.55</v>
       </c>
       <c r="I42" t="n">
         <v>384.0648745465496</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.35</v>
+        <v>-4.58</v>
       </c>
       <c r="L42" t="n">
-        <v>4.07</v>
+        <v>4.65</v>
       </c>
       <c r="M42" t="n">
         <v>0.37</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.14</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>398.15</v>
+        <v>403.25</v>
       </c>
       <c r="I43" t="n">
         <v>398.8717338946079</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.08</v>
+        <v>-5.41</v>
       </c>
       <c r="L43" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="M43" t="n">
         <v>1.74</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.73</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>456.7</v>
+        <v>452.6</v>
       </c>
       <c r="I44" t="n">
         <v>454.2555530018164</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K44" t="n">
-        <v>13.25</v>
+        <v>12.24</v>
       </c>
       <c r="L44" t="n">
         <v>1.5</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>4.69</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>468.75</v>
+        <v>473.8</v>
       </c>
       <c r="I45" t="n">
         <v>469.4187930443219</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.57</v>
+        <v>-4.68</v>
       </c>
       <c r="L45" t="n">
-        <v>3.87</v>
+        <v>5.79</v>
       </c>
       <c r="M45" t="n">
         <v>1.08</v>
       </c>
       <c r="N45" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="O45" t="n">
         <v>-0.92</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>3.94</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45847.55208333334</v>
+        <v>45848.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>462.15</v>
+        <v>453.4</v>
       </c>
       <c r="I46" t="n">
         <v>457.1007997379957</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.46</v>
+        <v>-4.31</v>
       </c>
       <c r="L46" t="n">
-        <v>3.69</v>
+        <v>4.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="N46" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
         <v>1.41</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>3.87</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45876.55208333334</v>
+        <v>45877.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>433.05</v>
+        <v>446.8</v>
       </c>
       <c r="I47" t="n">
         <v>446.0608022191152</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K47" t="n">
-        <v>4.49</v>
+        <v>1.46</v>
       </c>
       <c r="L47" t="n">
         <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="N47" t="n">
-        <v>1.29</v>
+        <v>2.77</v>
       </c>
       <c r="O47" t="n">
         <v>-2</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>4.42</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>433.85</v>
+        <v>427.2</v>
       </c>
       <c r="I48" t="n">
         <v>428.0273936078712</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.9</v>
+        <v>-4.39</v>
       </c>
       <c r="L48" t="n">
-        <v>3.65</v>
+        <v>4.41</v>
       </c>
       <c r="M48" t="n">
         <v>0.42</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.48</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45917.38541666666</v>
+        <v>45917.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>431.95</v>
+        <v>433.1</v>
       </c>
       <c r="I49" t="n">
         <v>432.4795014003625</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.11</v>
+        <v>-1.38</v>
       </c>
       <c r="L49" t="n">
         <v>4.07</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>2.51</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>432.25</v>
+        <v>428.4</v>
       </c>
       <c r="I50" t="n">
         <v>431.7775927481865</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.2</v>
+        <v>-1.09</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5</v>
+        <v>1.28</v>
       </c>
       <c r="M50" t="n">
         <v>0.5</v>
       </c>
       <c r="N50" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="O50" t="n">
         <v>0.39</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>3.8</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45930.38541666666</v>
+        <v>45930.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>439.5</v>
+        <v>441.65</v>
       </c>
       <c r="I51" t="n">
         <v>440.7478549401719</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.59</v>
+        <v>-3.09</v>
       </c>
       <c r="L51" t="n">
         <v>3.43</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>3.72</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45992.38541666666</v>
+        <v>45992.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>434.5</v>
+        <v>431.5</v>
       </c>
       <c r="I52" t="n">
         <v>433.3514998947895</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>61.83333333333334</v>
+        <v>62</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.62</v>
+        <v>-2.3</v>
       </c>
       <c r="L52" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="M52" t="n">
         <v>0.76</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>3.03</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>393.75</v>
+        <v>409.1</v>
       </c>
       <c r="I53" t="n">
         <v>407.2556338005052</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>63</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>8.75</v>
+        <v>5.19</v>
       </c>
       <c r="L53" t="n">
         <v>0.95</v>
       </c>
       <c r="M53" t="n">
-        <v>0.78</v>
+        <v>2.11</v>
       </c>
       <c r="N53" t="n">
-        <v>1.86</v>
+        <v>3.85</v>
       </c>
       <c r="O53" t="n">
         <v>-1.18</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.18</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080.38541666666</v>
+        <v>46080.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>416.85</v>
+        <v>413.3</v>
       </c>
       <c r="I54" t="n">
         <v>415.6177878518857</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>1.89</v>
+        <v>1.03</v>
       </c>
       <c r="L54" t="n">
         <v>1.81</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.68</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>361.8</v>
+        <v>387.9</v>
       </c>
       <c r="I55" t="n">
         <v>376.9776729271065</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>12.46</v>
+        <v>6.15</v>
       </c>
       <c r="L55" t="n">
         <v>1.02</v>
       </c>
       <c r="M55" t="n">
-        <v>2.67</v>
+        <v>5.32</v>
       </c>
       <c r="N55" t="n">
-        <v>3.03</v>
+        <v>7.32</v>
       </c>
       <c r="O55" t="n">
         <v>-2.76</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.97</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>390.05</v>
+        <v>384.2</v>
       </c>
       <c r="I56" t="n">
         <v>389.7110226684762</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K56" t="n">
-        <v>0.55</v>
+        <v>-0.95</v>
       </c>
       <c r="L56" t="n">
         <v>2.58</v>
@@ -3633,7 +4304,7 @@
         <v>0.77</v>
       </c>
       <c r="N56" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="O56" t="n">
         <v>7.32</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>4.12</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46163.55208333334</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>391.95</v>
+        <v>400.5</v>
       </c>
       <c r="I57" t="n">
         <v>395.6473662429882</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.02</v>
+        <v>-4.24</v>
       </c>
       <c r="L57" t="n">
-        <v>3.72</v>
+        <v>6.69</v>
       </c>
       <c r="M57" t="n">
-        <v>0.51</v>
+        <v>4.08</v>
       </c>
       <c r="N57" t="n">
         <v>2.22</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>4.13</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>402.05</v>
+        <v>395.35</v>
       </c>
       <c r="I58" t="n">
         <v>396.6942731762605</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>0.39</v>
+        <v>-1.29</v>
       </c>
       <c r="L58" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="M58" t="n">
         <v>0.08</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.04</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46188.55208333334</v>
+        <v>46189.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>396.9</v>
+        <v>399.65</v>
       </c>
       <c r="I59" t="n">
         <v>399.3321940440943</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.39</v>
+        <v>-1.09</v>
       </c>
       <c r="L59" t="n">
         <v>2.4</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>3.94</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>423.5</v>
+        <v>421</v>
       </c>
       <c r="I60" t="n">
         <v>423.3060688559485</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K60" t="n">
-        <v>5.97</v>
+        <v>5.34</v>
       </c>
       <c r="L60" t="n">
         <v>0.5600000000000001</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>405</v>
+        <v>409.85</v>
       </c>
       <c r="I61" t="n">
         <v>409.8498576325708</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="L61" t="n">
         <v>2.45</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.41</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46274.38541666666</v>
+        <v>46274.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>408.1</v>
+        <v>407.5</v>
       </c>
       <c r="I62" t="n">
         <v>407.9404415562851</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.43</v>
+        <v>-0.57</v>
       </c>
       <c r="L62" t="n">
         <v>1.26</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>3.51</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46288.38541666666</v>
+        <v>46288.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>404.5</v>
+        <v>407</v>
       </c>
       <c r="I63" t="n">
         <v>406.8556389697088</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="L63" t="n">
         <v>0.37</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>3.81</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>394</v>
+        <v>390.55</v>
       </c>
       <c r="I64" t="n">
         <v>391.4836960518024</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.19</v>
+        <v>-4.04</v>
       </c>
       <c r="L64" t="n">
-        <v>3.71</v>
+        <v>4.62</v>
       </c>
       <c r="M64" t="n">
         <v>1.5</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,12 @@
       <c r="Q65" t="n">
         <v>34</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6115,7 +6900,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6125,7 +6910,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="7">
@@ -6135,7 +6920,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="8">
@@ -6145,7 +6930,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6155,7 +6940,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.7</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="10">
@@ -6165,7 +6950,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -6205,7 +6990,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.32</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -6215,7 +7000,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.53</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="16">
@@ -6225,7 +7010,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="17">
@@ -6235,7 +7020,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.97</v>
+        <v>22.45</v>
       </c>
     </row>
     <row r="18">
@@ -6245,7 +7030,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="19">
@@ -6255,7 +7040,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="20">
@@ -6265,7 +7050,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="21">
@@ -6275,7 +7060,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.18</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="22">
@@ -6285,7 +7070,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -6295,7 +7080,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6305,7 +7090,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="25">
@@ -6315,7 +7100,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.25</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="26">
@@ -6325,7 +7110,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.77</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="27">
@@ -6335,7 +7120,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.16</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="28">
@@ -6345,7 +7130,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
